--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][CI]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][CI]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -495,40 +507,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1620</v>
+        <v>1560</v>
       </c>
       <c r="C2" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D2" t="n">
-        <v>10.15178260987932</v>
+        <v>10.26816475232522</v>
       </c>
       <c r="E2" t="n">
-        <v>12.18216457492928</v>
+        <v>12.25750881635532</v>
       </c>
       <c r="F2" t="n">
-        <v>4.453224226625171</v>
+        <v>4.446654560412027</v>
       </c>
       <c r="G2" t="n">
-        <v>3.163754210161873</v>
+        <v>3.181121315410964</v>
       </c>
       <c r="H2" t="n">
-        <v>10.23051414073535</v>
+        <v>10.35744430961875</v>
       </c>
       <c r="I2" t="n">
-        <v>11.82013680593205</v>
+        <v>11.9112585813085</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5896226651967</v>
+        <v>1.553814271689751</v>
       </c>
       <c r="K2" t="n">
-        <v>301434</v>
+        <v>275383</v>
       </c>
       <c r="L2" t="n">
-        <v>3.003886148749305e-20</v>
+        <v>1.725486263251748e-18</v>
       </c>
       <c r="M2" t="n">
-        <v>1.201554459499722e-19</v>
+        <v>6.901945053006993e-18</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -541,40 +553,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1620</v>
+        <v>1560</v>
       </c>
       <c r="C3" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D3" t="n">
-        <v>70.34564493910156</v>
+        <v>70.27127441526277</v>
       </c>
       <c r="E3" t="n">
-        <v>79.41566454608906</v>
+        <v>79.2705749975093</v>
       </c>
       <c r="F3" t="n">
-        <v>11.28999277311413</v>
+        <v>11.34825924157523</v>
       </c>
       <c r="G3" t="n">
-        <v>8.334265774267879</v>
+        <v>8.354842563260128</v>
       </c>
       <c r="H3" t="n">
-        <v>70.32867704017144</v>
+        <v>70.25791961122725</v>
       </c>
       <c r="I3" t="n">
-        <v>79.93609694043575</v>
+        <v>79.76082855786311</v>
       </c>
       <c r="J3" t="n">
-        <v>9.607419900264304</v>
+        <v>9.502908946635856</v>
       </c>
       <c r="K3" t="n">
-        <v>216951</v>
+        <v>198377</v>
       </c>
       <c r="L3" t="n">
-        <v>5.60285185935495e-59</v>
+        <v>7.572680891155814e-55</v>
       </c>
       <c r="M3" t="n">
-        <v>2.24114074374198e-58</v>
+        <v>3.029072356462326e-54</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -587,40 +599,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1620</v>
+        <v>1560</v>
       </c>
       <c r="C4" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D4" t="n">
-        <v>12.42646841858699</v>
+        <v>12.61026074751712</v>
       </c>
       <c r="E4" t="n">
-        <v>13.78095383772228</v>
+        <v>13.90090080317282</v>
       </c>
       <c r="F4" t="n">
-        <v>4.391029911561017</v>
+        <v>4.337491839194049</v>
       </c>
       <c r="G4" t="n">
-        <v>2.737742875728905</v>
+        <v>2.719485121783576</v>
       </c>
       <c r="H4" t="n">
-        <v>12.506223560039</v>
+        <v>12.82805347651585</v>
       </c>
       <c r="I4" t="n">
-        <v>13.6501355895433</v>
+        <v>13.70069693025265</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1439120295043</v>
+        <v>0.8726434537367993</v>
       </c>
       <c r="K4" t="n">
-        <v>337525</v>
+        <v>308834.5</v>
       </c>
       <c r="L4" t="n">
-        <v>4.397062209846633e-10</v>
+        <v>6.256208186126523e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.758824883938653e-09</v>
+        <v>2.502483274450609e-08</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -633,40 +645,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1620</v>
+        <v>1560</v>
       </c>
       <c r="C5" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D5" t="n">
-        <v>90.25084826311337</v>
+        <v>89.85479538345396</v>
       </c>
       <c r="E5" t="n">
-        <v>77.92639508721672</v>
+        <v>77.22390382347376</v>
       </c>
       <c r="F5" t="n">
-        <v>21.52824580126934</v>
+        <v>21.67945982181702</v>
       </c>
       <c r="G5" t="n">
-        <v>30.61024334208709</v>
+        <v>30.73248379761525</v>
       </c>
       <c r="H5" t="n">
-        <v>91.6649306538352</v>
+        <v>91.27113218228135</v>
       </c>
       <c r="I5" t="n">
-        <v>80.80611661477495</v>
+        <v>79.80439003679585</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.85881403906025</v>
+        <v>-11.4667421454855</v>
       </c>
       <c r="K5" t="n">
-        <v>506032</v>
+        <v>460571</v>
       </c>
       <c r="L5" t="n">
-        <v>1.690865559762685e-14</v>
+        <v>2.247206637509323e-14</v>
       </c>
       <c r="M5" t="n">
-        <v>6.76346223905074e-14</v>
+        <v>8.988826550037292e-14</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
